--- a/backend/df_out.xlsx
+++ b/backend/df_out.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,340 +472,236 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1388</v>
+        <v>978</v>
       </c>
       <c r="B2" t="n">
-        <v>2012.44600043426</v>
+        <v>1072.085</v>
       </c>
       <c r="C2" t="n">
-        <v>824.8886033349281</v>
+        <v>260.0167659407491</v>
       </c>
       <c r="D2" t="n">
-        <v>1876.044381444508</v>
+        <v>702.5683333333334</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>179.7067857659479</v>
+        <v>165.931765940749</v>
       </c>
       <c r="G2" t="n">
-        <v>99.99999991593813</v>
+        <v>99.99999983465609</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4098935320788695</v>
+        <v>0.1994919145353711</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1308</v>
+        <v>1082</v>
       </c>
       <c r="B3" t="n">
-        <v>1918.403003739863</v>
+        <v>1079.455</v>
       </c>
       <c r="C3" t="n">
-        <v>810.8456066405315</v>
+        <v>163.3867659407492</v>
       </c>
       <c r="D3" t="n">
-        <v>1293.957003305603</v>
+        <v>985.3700000000001</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>179.7067857659479</v>
+        <v>165.931765940749</v>
       </c>
       <c r="G3" t="n">
-        <v>99.99999991593813</v>
+        <v>99.99999983465609</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4226669791660798</v>
+        <v>0.1246499293879909</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1164</v>
+        <v>706</v>
       </c>
       <c r="B4" t="n">
-        <v>1908.82992040653</v>
+        <v>1090.013333333333</v>
       </c>
       <c r="C4" t="n">
-        <v>945.2725233071983</v>
+        <v>549.9450992740824</v>
       </c>
       <c r="D4" t="n">
-        <v>1298.426916666667</v>
+        <v>1092.558333333333</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>179.7067857659479</v>
+        <v>165.931765940749</v>
       </c>
       <c r="G4" t="n">
-        <v>99.99999991593813</v>
+        <v>99.99999983465609</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4952104471171407</v>
+        <v>0.4162078132115059</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1178</v>
+        <v>724</v>
       </c>
       <c r="B5" t="n">
-        <v>1903.363657780267</v>
+        <v>1100.258333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>925.8062606809353</v>
+        <v>542.1900992740825</v>
       </c>
       <c r="D5" t="n">
-        <v>1158.533737373737</v>
+        <v>716.2450000000001</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>179.7067857659479</v>
+        <v>165.931765940749</v>
       </c>
       <c r="G5" t="n">
-        <v>99.99999991593813</v>
+        <v>99.99999983465609</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4864053445764389</v>
+        <v>0.4071815780155982</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>976</v>
+        <v>586</v>
       </c>
       <c r="B6" t="n">
-        <v>1890.10190020451</v>
+        <v>1082.218333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>1114.544503105178</v>
+        <v>662.1500992740825</v>
       </c>
       <c r="D6" t="n">
-        <v>1164.738242424243</v>
+        <v>705.96</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>179.7067857659479</v>
+        <v>165.931765940749</v>
       </c>
       <c r="G6" t="n">
-        <v>99.99999991593813</v>
+        <v>99.99999983465609</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5896742906230829</v>
+        <v>0.5041003512674481</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>856</v>
+        <v>586</v>
       </c>
       <c r="B7" t="n">
-        <v>1890.10190020451</v>
+        <v>1078.933333333333</v>
       </c>
       <c r="C7" t="n">
-        <v>1234.544503105178</v>
+        <v>658.8650992740825</v>
       </c>
       <c r="D7" t="n">
-        <v>976</v>
+        <v>582.7149999999999</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>179.7067857659479</v>
+        <v>165.931765940749</v>
       </c>
       <c r="G7" t="n">
-        <v>99.99999991593813</v>
+        <v>99.99999983465609</v>
       </c>
       <c r="H7" t="n">
-        <v>0.65316293076049</v>
+        <v>0.5028570476060518</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>978</v>
+        <v>484</v>
       </c>
       <c r="B8" t="n">
-        <v>1900.574162830772</v>
+        <v>991.46</v>
       </c>
       <c r="C8" t="n">
-        <v>1123.016765731441</v>
+        <v>673.3917659407491</v>
       </c>
       <c r="D8" t="n">
-        <v>866.4722626262624</v>
+        <v>498.5266666666666</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>179.7067857659479</v>
+        <v>165.931765940749</v>
       </c>
       <c r="G8" t="n">
-        <v>99.99999991593813</v>
+        <v>99.99999983465609</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5908828930674068</v>
+        <v>0.5507100766568107</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1082</v>
+        <v>466</v>
       </c>
       <c r="B9" t="n">
-        <v>1930.338915522525</v>
+        <v>1010.19</v>
       </c>
       <c r="C9" t="n">
-        <v>1048.781518423193</v>
+        <v>710.1217659407491</v>
       </c>
       <c r="D9" t="n">
-        <v>1007.764752691753</v>
+        <v>502.73</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>179.7067857659479</v>
+        <v>165.931765940749</v>
       </c>
       <c r="G9" t="n">
-        <v>99.99999991593813</v>
+        <v>99.99999983465609</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5433147021781668</v>
+        <v>0.5719869192274506</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>706</v>
+        <v>436</v>
       </c>
       <c r="B10" t="n">
-        <v>1943.600673098282</v>
+        <v>1041.173333333333</v>
       </c>
       <c r="C10" t="n">
-        <v>1438.043275998951</v>
+        <v>771.1050992740825</v>
       </c>
       <c r="D10" t="n">
-        <v>1095.261757575758</v>
+        <v>496.9833333333333</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>179.7067857659479</v>
+        <v>165.931765940749</v>
       </c>
       <c r="G10" t="n">
-        <v>99.99999991593813</v>
+        <v>99.99999983465609</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7398861754393781</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>724</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1908.968997329607</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1385.411600230275</v>
-      </c>
-      <c r="D11" t="n">
-        <v>671.3683242313246</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>179.7067857659479</v>
-      </c>
-      <c r="G11" t="n">
-        <v>99.99999991593813</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.7257381313740036</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>586</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1903.502734703344</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1517.945337604013</v>
-      </c>
-      <c r="D12" t="n">
-        <v>718.5337373737375</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>179.7067857659479</v>
-      </c>
-      <c r="G12" t="n">
-        <v>99.99999991593813</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.7974484627499607</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>484</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1897.849358079967</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1614.291960980636</v>
-      </c>
-      <c r="D13" t="n">
-        <v>580.346623376623</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>179.7067857659479</v>
-      </c>
-      <c r="G13" t="n">
-        <v>99.99999991593813</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.8505901406779173</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>466</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1884.58760050421</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1619.030203404878</v>
-      </c>
-      <c r="D14" t="n">
-        <v>470.7382424242423</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>179.7067857659479</v>
-      </c>
-      <c r="G14" t="n">
-        <v>99.99999991593813</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.8590899114378219</v>
+        <v>0.6059844345420934</v>
       </c>
     </row>
   </sheetData>

--- a/backend/df_out.xlsx
+++ b/backend/df_out.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,236 +472,262 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>978</v>
+        <v>856.0000000000001</v>
       </c>
       <c r="B2" t="n">
-        <v>1072.085</v>
+        <v>1046.615495132601</v>
       </c>
       <c r="C2" t="n">
-        <v>260.0167659407491</v>
+        <v>247.3032011198167</v>
       </c>
       <c r="D2" t="n">
-        <v>702.5683333333334</v>
+        <v>1073.214295895267</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>165.931765940749</v>
+        <v>55.29821189916511</v>
       </c>
       <c r="G2" t="n">
-        <v>99.99999983465609</v>
+        <v>99.31316856630573</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1994919145353711</v>
+        <v>0.2289270486622527</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1082</v>
+        <v>977.9999999999999</v>
       </c>
       <c r="B3" t="n">
-        <v>1079.455</v>
+        <v>1049.394483308703</v>
       </c>
       <c r="C3" t="n">
-        <v>163.3867659407492</v>
+        <v>136.5492215460025</v>
       </c>
       <c r="D3" t="n">
-        <v>985.3700000000001</v>
+        <v>867.2460204261857</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>165.931765940749</v>
+        <v>55.29821189916511</v>
       </c>
       <c r="G3" t="n">
-        <v>99.99999983465609</v>
+        <v>99.31316856630573</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1246499293879909</v>
+        <v>0.1260784367666576</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>706</v>
+        <v>1082</v>
       </c>
       <c r="B4" t="n">
-        <v>1090.013333333333</v>
+        <v>1069.107535984972</v>
       </c>
       <c r="C4" t="n">
-        <v>549.9450992740824</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1092.558333333333</v>
+        <v>897.704006363772</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>47.74677209022548</v>
       </c>
       <c r="F4" t="n">
-        <v>165.931765940749</v>
+        <v>55.29821189916511</v>
       </c>
       <c r="G4" t="n">
-        <v>99.99999983465609</v>
+        <v>99.31316856630573</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4162078132115059</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>724</v>
+        <v>706.0000000000002</v>
       </c>
       <c r="B5" t="n">
-        <v>1100.258333333333</v>
+        <v>888.802496036247</v>
       </c>
       <c r="C5" t="n">
-        <v>542.1900992740825</v>
+        <v>273.0681328824437</v>
       </c>
       <c r="D5" t="n">
-        <v>716.2450000000001</v>
+        <v>979.0681328824439</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>165.931765940749</v>
+        <v>55.29821189916511</v>
       </c>
       <c r="G5" t="n">
-        <v>99.99999983465609</v>
+        <v>99.31316856630573</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4071815780155982</v>
+        <v>0.2960223643026866</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>586</v>
+        <v>724</v>
       </c>
       <c r="B6" t="n">
-        <v>1082.218333333333</v>
+        <v>958.7373459303105</v>
       </c>
       <c r="C6" t="n">
-        <v>662.1500992740825</v>
+        <v>149.8885484327623</v>
       </c>
       <c r="D6" t="n">
-        <v>705.96</v>
+        <v>600.8204155503186</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>165.931765940749</v>
+        <v>55.29821189916511</v>
       </c>
       <c r="G6" t="n">
-        <v>99.99999983465609</v>
+        <v>99.31316856630573</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5041003512674481</v>
+        <v>0.1510375470153356</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>586</v>
+        <v>586.0000000000002</v>
       </c>
       <c r="B7" t="n">
-        <v>1078.933333333333</v>
+        <v>678.4433271368838</v>
       </c>
       <c r="C7" t="n">
-        <v>658.8650992740825</v>
+        <v>118.0150525520468</v>
       </c>
       <c r="D7" t="n">
-        <v>582.7149999999999</v>
+        <v>554.1265041192847</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>165.931765940749</v>
+        <v>55.29821189916511</v>
       </c>
       <c r="G7" t="n">
-        <v>99.99999983465609</v>
+        <v>99.31316856630573</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5028570476060518</v>
+        <v>0.1657285252084081</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>484</v>
+        <v>586.0000000000002</v>
       </c>
       <c r="B8" t="n">
-        <v>991.46</v>
+        <v>618.9903541688799</v>
       </c>
       <c r="C8" t="n">
-        <v>673.3917659407491</v>
+        <v>45.26546581397429</v>
       </c>
       <c r="D8" t="n">
-        <v>498.5266666666666</v>
+        <v>513.2504132619277</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>165.931765940749</v>
+        <v>55.29821189916511</v>
       </c>
       <c r="G8" t="n">
-        <v>99.99999983465609</v>
+        <v>99.31316856630573</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5507100766568107</v>
+        <v>0.06935688097480475</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>466</v>
+        <v>484.0000000000001</v>
       </c>
       <c r="B9" t="n">
-        <v>1010.19</v>
+        <v>532.9441536607389</v>
       </c>
       <c r="C9" t="n">
-        <v>710.1217659407491</v>
+        <v>89.89348098739873</v>
       </c>
       <c r="D9" t="n">
-        <v>502.73</v>
+        <v>528.6280151734245</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>165.931765940749</v>
+        <v>55.29821189916511</v>
       </c>
       <c r="G9" t="n">
-        <v>99.99999983465609</v>
+        <v>99.31316856630573</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5719869192274506</v>
+        <v>0.1586543774733911</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>436</v>
+        <v>466.0000000000001</v>
       </c>
       <c r="B10" t="n">
-        <v>1041.173333333333</v>
+        <v>504.2463845157284</v>
       </c>
       <c r="C10" t="n">
-        <v>771.1050992740825</v>
+        <v>37.98168394186217</v>
       </c>
       <c r="D10" t="n">
-        <v>496.9833333333333</v>
+        <v>414.0882029544635</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>165.931765940749</v>
+        <v>55.29821189916511</v>
       </c>
       <c r="G10" t="n">
-        <v>99.99999983465609</v>
+        <v>99.31316856630573</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6059844345420934</v>
+        <v>0.07061083130391221</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>435.9999999999999</v>
+      </c>
+      <c r="B11" t="n">
+        <v>393.1205595696659</v>
+      </c>
+      <c r="C11" t="n">
+        <v>12.4187714688311</v>
+      </c>
+      <c r="D11" t="n">
+        <v>410.4370875269688</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>55.29821189916511</v>
+      </c>
+      <c r="G11" t="n">
+        <v>99.31316856630573</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.02909904969798667</v>
       </c>
     </row>
   </sheetData>

--- a/backend/df_out.xlsx
+++ b/backend/df_out.xlsx
@@ -475,25 +475,25 @@
         <v>856.0000000000001</v>
       </c>
       <c r="B2" t="n">
-        <v>1046.615495132601</v>
+        <v>1639.72541255639</v>
       </c>
       <c r="C2" t="n">
-        <v>247.3032011198167</v>
+        <v>1168.524240057322</v>
       </c>
       <c r="D2" t="n">
-        <v>1073.214295895267</v>
+        <v>1637.300167143748</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>55.29821189916511</v>
+        <v>384.7988275009323</v>
       </c>
       <c r="G2" t="n">
-        <v>99.31316856630573</v>
+        <v>99.99999985515643</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2289270486622527</v>
+        <v>0.7393149882113409</v>
       </c>
     </row>
     <row r="3">
@@ -501,25 +501,25 @@
         <v>977.9999999999999</v>
       </c>
       <c r="B3" t="n">
-        <v>1049.394483308703</v>
+        <v>1663.143062844016</v>
       </c>
       <c r="C3" t="n">
-        <v>136.5492215460025</v>
+        <v>1069.941890344948</v>
       </c>
       <c r="D3" t="n">
-        <v>867.2460204261857</v>
+        <v>879.417650287626</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>55.29821189916511</v>
+        <v>384.7988275009323</v>
       </c>
       <c r="G3" t="n">
-        <v>99.31316856630573</v>
+        <v>99.99999985515643</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1260784367666576</v>
+        <v>0.6670595559726828</v>
       </c>
     </row>
     <row r="4">
@@ -527,25 +527,25 @@
         <v>1082</v>
       </c>
       <c r="B4" t="n">
-        <v>1069.107535984972</v>
+        <v>1633.744665300598</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>936.54349280153</v>
       </c>
       <c r="D4" t="n">
-        <v>897.704006363772</v>
+        <v>948.6016024565818</v>
       </c>
       <c r="E4" t="n">
-        <v>47.74677209022548</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>55.29821189916511</v>
+        <v>384.7988275009323</v>
       </c>
       <c r="G4" t="n">
-        <v>99.31316856630573</v>
+        <v>99.99999985515643</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.5947934923212665</v>
       </c>
     </row>
     <row r="5">
@@ -553,25 +553,25 @@
         <v>706.0000000000002</v>
       </c>
       <c r="B5" t="n">
-        <v>888.802496036247</v>
+        <v>1667.897429540901</v>
       </c>
       <c r="C5" t="n">
-        <v>273.0681328824437</v>
+        <v>1346.696257041833</v>
       </c>
       <c r="D5" t="n">
-        <v>979.0681328824439</v>
+        <v>1116.152764240303</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>55.29821189916511</v>
+        <v>384.7988275009323</v>
       </c>
       <c r="G5" t="n">
-        <v>99.31316856630573</v>
+        <v>99.99999985515643</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2960223643026866</v>
+        <v>0.8371218370388102</v>
       </c>
     </row>
     <row r="6">
@@ -579,25 +579,25 @@
         <v>724</v>
       </c>
       <c r="B6" t="n">
-        <v>958.7373459303105</v>
+        <v>1743.999845769459</v>
       </c>
       <c r="C6" t="n">
-        <v>149.8885484327623</v>
+        <v>1404.798673270391</v>
       </c>
       <c r="D6" t="n">
-        <v>600.8204155503186</v>
+        <v>782.1024162285582</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>55.29821189916511</v>
+        <v>384.7988275009323</v>
       </c>
       <c r="G6" t="n">
-        <v>99.31316856630573</v>
+        <v>99.99999985515643</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1510375470153356</v>
+        <v>0.8337953310671579</v>
       </c>
     </row>
     <row r="7">
@@ -605,25 +605,25 @@
         <v>586.0000000000002</v>
       </c>
       <c r="B7" t="n">
-        <v>678.4433271368838</v>
+        <v>1663.017676393966</v>
       </c>
       <c r="C7" t="n">
-        <v>118.0150525520468</v>
+        <v>1461.816503894898</v>
       </c>
       <c r="D7" t="n">
-        <v>554.1265041192847</v>
+        <v>643.0178306245066</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>55.29821189916511</v>
+        <v>384.7988275009323</v>
       </c>
       <c r="G7" t="n">
-        <v>99.31316856630573</v>
+        <v>99.99999985515643</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1657285252084081</v>
+        <v>0.9114466032267576</v>
       </c>
     </row>
     <row r="8">
@@ -631,25 +631,25 @@
         <v>586.0000000000002</v>
       </c>
       <c r="B8" t="n">
-        <v>618.9903541688799</v>
+        <v>1638.942333761433</v>
       </c>
       <c r="C8" t="n">
-        <v>45.26546581397429</v>
+        <v>1437.741161262365</v>
       </c>
       <c r="D8" t="n">
-        <v>513.2504132619277</v>
+        <v>561.9246573674675</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>55.29821189916511</v>
+        <v>384.7988275009323</v>
       </c>
       <c r="G8" t="n">
-        <v>99.31316856630573</v>
+        <v>99.99999985515643</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06935688097480475</v>
+        <v>0.9100970664958509</v>
       </c>
     </row>
     <row r="9">
@@ -657,25 +657,25 @@
         <v>484.0000000000001</v>
       </c>
       <c r="B9" t="n">
-        <v>532.9441536607389</v>
+        <v>1602.701317795769</v>
       </c>
       <c r="C9" t="n">
-        <v>89.89348098739873</v>
+        <v>1503.500145296702</v>
       </c>
       <c r="D9" t="n">
-        <v>528.6280151734245</v>
+        <v>549.7589840343369</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>55.29821189916511</v>
+        <v>384.7988275009323</v>
       </c>
       <c r="G9" t="n">
-        <v>99.31316856630573</v>
+        <v>99.99999985515643</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1586543774733911</v>
+        <v>0.974068673064044</v>
       </c>
     </row>
     <row r="10">
@@ -683,25 +683,25 @@
         <v>466.0000000000001</v>
       </c>
       <c r="B10" t="n">
-        <v>504.2463845157284</v>
+        <v>1558.375656062057</v>
       </c>
       <c r="C10" t="n">
-        <v>37.98168394186217</v>
+        <v>1477.17448356299</v>
       </c>
       <c r="D10" t="n">
-        <v>414.0882029544635</v>
+        <v>439.6743382662878</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>55.29821189916511</v>
+        <v>384.7988275009323</v>
       </c>
       <c r="G10" t="n">
-        <v>99.31316856630573</v>
+        <v>99.99999985515643</v>
       </c>
       <c r="H10" t="n">
-        <v>0.07061083130391221</v>
+        <v>0.985308384255677</v>
       </c>
     </row>
     <row r="11">
@@ -709,25 +709,25 @@
         <v>435.9999999999999</v>
       </c>
       <c r="B11" t="n">
-        <v>393.1205595696659</v>
+        <v>1494.835983735028</v>
       </c>
       <c r="C11" t="n">
-        <v>12.4187714688311</v>
+        <v>1443.634811235961</v>
       </c>
       <c r="D11" t="n">
-        <v>410.4370875269688</v>
+        <v>402.4603276729708</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>55.29821189916511</v>
+        <v>384.7988275009323</v>
       </c>
       <c r="G11" t="n">
-        <v>99.31316856630573</v>
+        <v>99.99999985515643</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02909904969798667</v>
+        <v>1.005554466025383</v>
       </c>
     </row>
   </sheetData>
